--- a/resampling/input/accessibility_reports_generated/CARE_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/CARE_accessibility_report.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -87,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +106,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -181,9 +184,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:O138" headerRowCount="1">
-  <autoFilter ref="A1:O138"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q138" headerRowCount="1">
+  <autoFilter ref="A1:Q138"/>
+  <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
@@ -199,15 +202,17 @@
     <tableColumn id="13" name="Reason notes"/>
     <tableColumn id="14" name="% of target achieved so far"/>
     <tableColumn id="15" name="Date reported"/>
+    <tableColumn id="16" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="17" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M224" headerRowCount="1">
-  <autoFilter ref="A1:M224"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O224" headerRowCount="1">
+  <autoFilter ref="A1:O224"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
@@ -221,6 +226,8 @@
     <tableColumn id="11" name="Reason notes"/>
     <tableColumn id="12" name="% of target achieved so far"/>
     <tableColumn id="13" name="Date reported"/>
+    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="15" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -515,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -613,58 +620,78 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Ward Accessibility</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -684,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:Q138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -702,6 +729,8 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -780,6 +809,16 @@
           <t>Date reported</t>
         </is>
       </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Reported by (Partner / IMPACT-default)</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Source channel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -822,7 +861,9 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -865,7 +906,9 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -908,7 +951,9 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -951,7 +996,9 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -994,7 +1041,9 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1037,7 +1086,9 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1088,7 +1139,9 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1131,7 +1184,9 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1170,7 +1225,9 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1209,7 +1266,9 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1248,7 +1307,9 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1295,7 +1356,9 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1342,7 +1405,9 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1389,7 +1454,9 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1436,7 +1503,9 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1475,7 +1544,9 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1522,7 +1593,9 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1561,7 +1634,9 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1608,7 +1683,9 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1647,7 +1724,9 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1686,7 +1765,9 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" s="10" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1725,7 +1806,9 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" s="10" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1764,7 +1847,9 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" s="10" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1803,7 +1888,9 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" s="10" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1842,7 +1929,9 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" s="10" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1881,7 +1970,9 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1920,7 +2011,9 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1959,7 +2052,9 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1998,7 +2093,9 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2037,7 +2134,9 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2076,7 +2175,9 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2115,7 +2216,9 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2154,7 +2257,9 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2193,7 +2298,9 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2232,7 +2339,9 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2271,7 +2380,9 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2318,7 +2429,9 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2357,7 +2470,9 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2396,7 +2511,9 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2435,7 +2552,9 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2474,7 +2593,9 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2513,7 +2634,9 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2552,7 +2675,9 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2591,7 +2716,9 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2638,7 +2765,9 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" s="10" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2677,7 +2806,9 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" s="10" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2716,7 +2847,9 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" s="10" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2763,7 +2896,9 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" s="10" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2802,7 +2937,9 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" s="10" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2849,7 +2986,9 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" s="10" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2888,7 +3027,9 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" s="10" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2935,7 +3076,9 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" s="10" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2974,7 +3117,9 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" s="10" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3013,7 +3158,9 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" s="10" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3060,7 +3207,9 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3099,7 +3248,9 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3146,7 +3297,9 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" s="10" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3185,7 +3338,9 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3224,7 +3379,9 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" s="10" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3271,7 +3428,9 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3310,7 +3469,9 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" s="10" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3349,7 +3510,9 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3396,7 +3559,9 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" s="10" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3435,7 +3600,9 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3482,7 +3649,9 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" s="10" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3521,7 +3690,9 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3568,7 +3739,9 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" s="10" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3607,7 +3780,9 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3646,7 +3821,9 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" s="10" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3685,7 +3862,9 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" s="10" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3732,7 +3911,9 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" s="10" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3771,7 +3952,9 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" s="10" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3810,7 +3993,9 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" s="10" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3849,7 +4034,9 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" s="10" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3888,7 +4075,9 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" s="10" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3927,7 +4116,9 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" s="10" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3966,7 +4157,9 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="O78" s="10" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4005,7 +4198,9 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="O79" s="10" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4052,7 +4247,9 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="O80" s="10" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4099,7 +4296,9 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" s="10" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4138,7 +4337,9 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="O82" s="10" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4185,7 +4386,9 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4224,7 +4427,9 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" s="10" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4263,7 +4468,9 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4302,7 +4509,9 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" s="10" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4341,7 +4550,9 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4380,7 +4591,9 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" s="10" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4419,7 +4632,9 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4458,7 +4673,9 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" s="10" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4497,7 +4714,9 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4536,7 +4755,9 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="O92" s="10" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4575,7 +4796,9 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4622,7 +4845,9 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" s="10" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4669,7 +4894,9 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4708,7 +4935,9 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" s="10" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4747,7 +4976,9 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="O97" s="10" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4786,7 +5017,9 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" s="10" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4825,7 +5058,9 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="O99" s="10" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4864,7 +5099,9 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+      <c r="O100" s="10" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4903,7 +5140,9 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="O101" s="10" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4942,7 +5181,9 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" s="10" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4981,7 +5222,9 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
+      <c r="O103" s="10" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5028,7 +5271,9 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" s="10" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5067,7 +5312,9 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5106,7 +5353,9 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="O106" s="10" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5145,7 +5394,9 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" s="10" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5192,7 +5443,9 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" s="10" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5231,7 +5484,9 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="O109" s="10" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5270,7 +5525,9 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" s="10" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5309,7 +5566,9 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" s="10" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5356,7 +5615,9 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" s="10" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5395,7 +5656,9 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+      <c r="O113" s="10" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5434,7 +5697,9 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="O114" s="10" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5473,7 +5738,9 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="O115" s="10" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5512,7 +5779,9 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" s="10" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5551,7 +5820,9 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" s="10" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5590,7 +5861,9 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
+      <c r="O118" s="10" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5637,7 +5910,9 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
+      <c r="O119" s="10" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5684,7 +5959,9 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="O120" s="10" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5723,7 +6000,9 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" s="10" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5770,7 +6049,9 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+      <c r="O122" s="10" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5809,7 +6090,9 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="O123" s="10" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5848,7 +6131,9 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" s="10" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5887,7 +6172,9 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="O125" s="10" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5926,7 +6213,9 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="O126" s="10" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5965,7 +6254,9 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
+      <c r="O127" s="10" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6004,7 +6295,9 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="O128" s="10" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6051,7 +6344,9 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" s="10" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6098,7 +6393,9 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" s="10" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6145,7 +6442,9 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+      <c r="O131" s="10" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6184,7 +6483,9 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" s="10" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6223,7 +6524,9 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" s="10" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6270,7 +6573,9 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="O134" s="10" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6309,7 +6614,9 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
+      <c r="O135" s="10" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6356,7 +6663,9 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
+      <c r="O136" s="10" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6395,7 +6704,9 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
+      <c r="O137" s="10" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6442,15 +6753,27 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" s="10" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="K2:K138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O138" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-08-28</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M224"/>
+  <dimension ref="A1:O224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6482,6 +6805,8 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6550,6 +6875,16 @@
           <t>Date reported</t>
         </is>
       </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Reported by (Partner / IMPACT-default)</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Source channel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6596,7 +6931,9 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6643,7 +6980,9 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6686,7 +7025,9 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6729,7 +7070,9 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6772,7 +7115,9 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6815,7 +7160,9 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6858,7 +7205,9 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6901,7 +7250,9 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6944,7 +7295,9 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6987,7 +7340,9 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7030,7 +7385,9 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7073,7 +7430,9 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7116,7 +7475,9 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7159,7 +7520,9 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7202,7 +7565,9 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7245,7 +7610,9 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7288,7 +7655,9 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7331,7 +7700,9 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7374,7 +7745,9 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7421,7 +7794,9 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7468,7 +7843,9 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7515,7 +7892,9 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7562,7 +7941,9 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7609,7 +7990,9 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7652,7 +8035,9 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7695,7 +8080,9 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7738,7 +8125,9 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7781,7 +8170,9 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7824,7 +8215,9 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7867,7 +8260,9 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7910,7 +8305,9 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7953,7 +8350,9 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7996,7 +8395,9 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8039,7 +8440,9 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8082,7 +8485,9 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8125,7 +8530,9 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8168,7 +8575,9 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8211,7 +8620,9 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8254,7 +8665,9 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8297,7 +8710,9 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8340,7 +8755,9 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8383,7 +8800,9 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8426,7 +8845,9 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8469,7 +8890,9 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8512,7 +8935,9 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" s="10" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8555,7 +8980,9 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" s="10" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8598,7 +9025,9 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8641,7 +9070,9 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8684,7 +9115,9 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" s="10" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8727,7 +9160,9 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8770,7 +9205,9 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" s="10" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8813,7 +9250,9 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" s="10" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8856,7 +9295,9 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" s="10" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8899,7 +9340,9 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8942,7 +9385,9 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8985,7 +9430,9 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9028,7 +9475,9 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" s="10" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9071,7 +9520,9 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9114,7 +9565,9 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" s="10" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9157,7 +9610,9 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" s="10" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9200,7 +9655,9 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" s="10" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9243,7 +9700,9 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" s="10" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9286,7 +9745,9 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" s="10" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9329,7 +9790,9 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" s="10" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9372,7 +9835,9 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" s="10" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9415,7 +9880,9 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9458,7 +9925,9 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" s="10" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9501,7 +9970,9 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" s="10" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9544,7 +10015,9 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" s="10" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9587,7 +10060,9 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" s="10" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9630,7 +10105,9 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" s="10" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9673,7 +10150,9 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" s="10" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9716,7 +10195,9 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" s="10" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9759,7 +10240,9 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" s="10" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9802,7 +10285,9 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" s="10" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9849,7 +10334,9 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9896,7 +10383,9 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" s="10" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9943,7 +10432,9 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="M79" s="10" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9990,7 +10481,9 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="M80" s="10" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10037,7 +10530,9 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10084,7 +10579,9 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="M82" s="10" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10131,7 +10628,9 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
+      <c r="M83" s="10" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10174,7 +10673,9 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="M84" s="10" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10217,7 +10718,9 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10260,7 +10763,9 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="M86" s="10" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10303,7 +10808,9 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10346,7 +10853,9 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="M88" s="10" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10389,7 +10898,9 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
+      <c r="M89" s="10" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10432,7 +10943,9 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" s="10" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10475,7 +10988,9 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="M91" s="10" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10518,7 +11033,9 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
+      <c r="M92" s="10" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10561,7 +11078,9 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10604,7 +11123,9 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="M94" s="10" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10647,7 +11168,9 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10694,7 +11217,9 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" s="10" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10741,7 +11266,9 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="M97" s="10" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10788,7 +11315,9 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
+      <c r="M98" s="10" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10835,7 +11364,9 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="M99" s="10" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10882,7 +11413,9 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="M100" s="10" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10929,7 +11462,9 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
+      <c r="M101" s="10" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10976,7 +11511,9 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
+      <c r="M102" s="10" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11019,7 +11556,9 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
+      <c r="M103" s="10" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11062,7 +11601,9 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
+      <c r="M104" s="10" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11105,7 +11646,9 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
+      <c r="M105" s="10" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11148,7 +11691,9 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
+      <c r="M106" s="10" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11191,7 +11736,9 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+      <c r="M107" s="10" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11234,7 +11781,9 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+      <c r="M108" s="10" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11277,7 +11826,9 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+      <c r="M109" s="10" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11320,7 +11871,9 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
+      <c r="M110" s="10" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11363,7 +11916,9 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
+      <c r="M111" s="10" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11406,7 +11961,9 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
+      <c r="M112" s="10" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11449,7 +12006,9 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
+      <c r="M113" s="10" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11492,7 +12051,9 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
+      <c r="M114" s="10" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11535,7 +12096,9 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
+      <c r="M115" s="10" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11578,7 +12141,9 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
+      <c r="M116" s="10" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11621,7 +12186,9 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
+      <c r="M117" s="10" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11664,7 +12231,9 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
+      <c r="M118" s="10" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11707,7 +12276,9 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
+      <c r="M119" s="10" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11754,7 +12325,9 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
+      <c r="M120" s="10" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11801,7 +12374,9 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
+      <c r="M121" s="10" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11848,7 +12423,9 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
+      <c r="M122" s="10" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11891,7 +12468,9 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" s="10" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11934,7 +12513,9 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
+      <c r="M124" s="10" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11977,7 +12558,9 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
+      <c r="M125" s="10" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12020,7 +12603,9 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
+      <c r="M126" s="10" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12063,7 +12648,9 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
+      <c r="M127" s="10" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12106,7 +12693,9 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
+      <c r="M128" s="10" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12149,7 +12738,9 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
+      <c r="M129" s="10" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12192,7 +12783,9 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
+      <c r="M130" s="10" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12235,7 +12828,9 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
+      <c r="M131" s="10" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12278,7 +12873,9 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
+      <c r="M132" s="10" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12321,7 +12918,9 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" s="10" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12364,7 +12963,9 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" s="10" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12407,7 +13008,9 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
+      <c r="M135" s="10" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12450,7 +13053,9 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
+      <c r="M136" s="10" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12493,7 +13098,9 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" s="10" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12540,7 +13147,9 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
+      <c r="M138" s="10" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12587,7 +13196,9 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
+      <c r="M139" s="10" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12634,7 +13245,9 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
+      <c r="M140" s="10" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12681,7 +13294,9 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
+      <c r="M141" s="10" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12724,7 +13339,9 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
+      <c r="M142" s="10" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12767,7 +13384,9 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
+      <c r="M143" s="10" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12810,7 +13429,9 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
+      <c r="M144" s="10" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12853,7 +13474,9 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+      <c r="M145" s="10" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12896,7 +13519,9 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
+      <c r="M146" s="10" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12939,7 +13564,9 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
+      <c r="M147" s="10" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12982,7 +13609,9 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
+      <c r="M148" s="10" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13025,7 +13654,9 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" s="10" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13068,7 +13699,9 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="M150" s="10" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13111,7 +13744,9 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" s="10" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13154,7 +13789,9 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
+      <c r="M152" s="10" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13197,7 +13834,9 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" s="10" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13240,7 +13879,9 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
+      <c r="M154" s="10" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13283,7 +13924,9 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" s="10" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13326,7 +13969,9 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
+      <c r="M156" s="10" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13369,7 +14014,9 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="M157" s="10" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13412,7 +14059,9 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
+      <c r="M158" s="10" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13459,7 +14108,9 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" s="10" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13506,7 +14157,9 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
+      <c r="M160" s="10" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13553,7 +14206,9 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
+      <c r="M161" s="10" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13600,7 +14255,9 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
+      <c r="M162" s="10" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13647,7 +14304,9 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+      <c r="M163" s="10" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13694,7 +14353,9 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
+      <c r="M164" s="10" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13741,7 +14402,9 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" s="10" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13788,7 +14451,9 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+      <c r="M166" s="10" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13835,7 +14500,9 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
+      <c r="M167" s="10" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13882,7 +14549,9 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" s="10" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13929,7 +14598,9 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
+      <c r="M169" s="10" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13976,7 +14647,9 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
+      <c r="M170" s="10" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14023,7 +14696,9 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
+      <c r="M171" s="10" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14066,7 +14741,9 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
+      <c r="M172" s="10" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14109,7 +14786,9 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
+      <c r="M173" s="10" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14152,7 +14831,9 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
+      <c r="M174" s="10" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14195,7 +14876,9 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" s="10" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14238,7 +14921,9 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
+      <c r="M176" s="10" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14281,7 +14966,9 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
+      <c r="M177" s="10" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14324,7 +15011,9 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
+      <c r="M178" s="10" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14367,7 +15056,9 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" s="10" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14410,7 +15101,9 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" s="10" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14453,7 +15146,9 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
+      <c r="M181" s="10" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14496,7 +15191,9 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" s="10" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14539,7 +15236,9 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
+      <c r="M183" s="10" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14582,7 +15281,9 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
+      <c r="M184" s="10" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14625,7 +15326,9 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
+      <c r="M185" s="10" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14672,7 +15375,9 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
+      <c r="M186" s="10" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14719,7 +15424,9 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
+      <c r="M187" s="10" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14766,7 +15473,9 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
+      <c r="M188" s="10" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14813,7 +15522,9 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" s="10" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14856,7 +15567,9 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" s="10" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -14899,7 +15612,9 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
+      <c r="M191" s="10" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -14942,7 +15657,9 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" s="10" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14985,7 +15702,9 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
+      <c r="M193" s="10" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15028,7 +15747,9 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
+      <c r="M194" s="10" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15071,7 +15792,9 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
+      <c r="M195" s="10" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15114,7 +15837,9 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" s="10" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15157,7 +15882,9 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
+      <c r="M197" s="10" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15200,7 +15927,9 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
+      <c r="M198" s="10" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15243,7 +15972,9 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
+      <c r="M199" s="10" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15286,7 +16017,9 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
+      <c r="M200" s="10" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15329,7 +16062,9 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
+      <c r="M201" s="10" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15372,7 +16107,9 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
+      <c r="M202" s="10" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15415,7 +16152,9 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
+      <c r="M203" s="10" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15462,7 +16201,9 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" s="10" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15509,7 +16250,9 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
+      <c r="M205" s="10" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15556,7 +16299,9 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" s="10" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15603,7 +16348,9 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
+      <c r="M207" s="10" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15646,7 +16393,9 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
+      <c r="M208" s="10" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15689,7 +16438,9 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
+      <c r="M209" s="10" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15732,7 +16483,9 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
+      <c r="M210" s="10" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15775,7 +16528,9 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
+      <c r="M211" s="10" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15818,7 +16573,9 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
+      <c r="M212" s="10" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15861,7 +16618,9 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
+      <c r="M213" s="10" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15904,7 +16663,9 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
+      <c r="M214" s="10" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15947,7 +16708,9 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
+      <c r="M215" s="10" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15990,7 +16753,9 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
+      <c r="M216" s="10" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16033,7 +16798,9 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
+      <c r="M217" s="10" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -16076,7 +16843,9 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
+      <c r="M218" s="10" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16119,7 +16888,9 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
+      <c r="M219" s="10" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16162,7 +16933,9 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
+      <c r="M220" s="10" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16205,7 +16978,9 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
+      <c r="M221" s="10" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16248,7 +17023,9 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" s="10" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16291,7 +17068,9 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
+      <c r="M223" s="10" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16334,15 +17113,27 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
+      <c r="M224" s="10" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="I2:I224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M224" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-08-28</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16350,4 +17141,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F883E8D7-F4B6-465E-A45C-DCD3DC32E670}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D93926B-3C30-4D16-AF1E-B07849E1337C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52F0A829-CA50-48C0-93AC-F9ED6F468462}"/>
 </file>